--- a/medford_massazhery.xlsx
+++ b/medford_massazhery.xlsx
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Массажеры для оснащения клиник и медицинских учреждений. В каталоге представлено 1 позиций.</t>
+          <t>Массажеры для оснащения клиник и медицинских учреждений.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">

--- a/medford_massazhery.xlsx
+++ b/medford_massazhery.xlsx
@@ -941,7 +941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1022,12 +1022,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать массажеры для клиники?</t>
+          <t>Что даёт пневмомассаж барабанной перепонки?</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Выбор зависит от задач отделения, совместимости с оборудованием и ключевых характеристик (Страна производства, Полная потребляемая мощность, ВА, Производитель, Скорость). Учитывайте бренд, гарантию, сервис и наличие РУ. Поможем сравнить модели и подобрать оптимальную.</t>
+          <t>Пневмомассаж воздействует на барабанную перепонку переменным давлением или звуковыми колебаниями, восстанавливая её подвижность и подвижность слуховых косточек и улучшая вентиляцию среднего уха. Процедуру применяют в составе лечебных схем при ряде состояний уха по назначению врача-оториноларинголога.</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Нужно ли регистрационное удостоверение (РУ)?</t>
+          <t>Чем аппарат отличается от бытового массажёра?</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Да. Это медицинское изделие; для закупки в клинику с медицинской лицензией необходимо действующее регистрационное удостоверение Росздравнадзора. Проверяйте наличие РУ на конкретную модель.</t>
+          <t>Аппарат для пневмомассажа барабанной перепонки — профессиональное медицинское оборудование с дозируемым режимом и таймером, рассчитанное на применение в ЛПУ и физиокабинетах. Он воздействует направленно на структуры среднего уха по медицинскому протоколу, тогда как бытовые массажёры такой задачи не решают.</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1098,12 +1098,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>Какие бренды представлены в каталоге?</t>
+          <t>Можно ли делать массаж ушей при отите?</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>В каталоге представлены модели ведущих производителей. Подберём под ваши задачи и бюджет.</t>
+          <t>Пневмомассаж имеет противопоказания, к которым относят острый гнойный отит и перфорацию барабанной перепонки. Проводить процедуру при воспалении без назначения нельзя. Решение о допустимости массажа в конкретной ситуации принимает врач-оториноларинголог после осмотра.</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1136,12 +1136,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>Сколько стоит оборудование?</t>
+          <t>На что смотреть при выборе аппарата?</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Цена указывается по запросу и зависит от модели, комплектации и условий поставки. Отправьте запрос — подготовим коммерческое предложение за 1 день.</t>
+          <t>Оценивайте назначение и формат применения (ЛПУ или физиокабинет), настраиваемый режим и таймер процедуры, электропитание и компактность размещения, а также наличие регистрационного удостоверения. Chammed XCM3 extreme имеет таймер 1–10 минут и мощность 30 ВА, что подходит для профессионального кабинета.</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1174,12 +1174,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>Есть ли гарантия, сервис и обучение?</t>
+          <t>Нужно ли регистрационное удостоверение?</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Да. Обеспечиваем доставку по России, монтаж и ввод в эксплуатацию, обучение персонала, гарантийное и постгарантийное обслуживание, поставку расходных материалов. Телефон: +7 (499) 495-48-21.</t>
+          <t>Да. Для законного применения в медицинской организации аппарат должен иметь действующее регистрационное удостоверение Росздравнадзора. Перед закупкой проверьте наличие РУ на конкретную модель и её нахождение в реестре медицинских изделий.</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Что дает пневмомассаж барабанной перепонки?</t>
+          <t>Кто назначает процедуру пневмомассажа?</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
+          <t>Показания, режим и курс определяет врач-оториноларинголог после осмотра пациента. Процедуру проводят в кабинете под контролем медперсонала. Из-за противопоказаний самостоятельное применение прибора без консультации специалиста не рекомендуется.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1226,44 +1226,6 @@
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>FAQ</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="n">
-        <v>22</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>FAQ_07</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>170</v>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Как массировать барабанную перепонку?</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Зависит от модели и клинической задачи. Подберём вариант под ваши требования и ответим на вопрос при консультации — напишите или позвоните: +7 (499) 495-48-21.</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>massazhery</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
         <is>
           <t>FAQ</t>
         </is>
@@ -2148,7 +2110,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Массажеры для оснащения клиник и медицинских учреждений.</t>
+          <t>Массажеры в ЛОР-практике — аппараты для пневмомассажа барабанной перепонки, которые воздействуют на неё переменным давлением или колебаниями воздуха для восстановления подвижности перепонки и слуховых косточек. В категории представлен аппарат для массажа барабанных перепонок Chammed XCM3 extreme (Южная Корея) с таймером процедуры от 1 до 10 минут и полной потребляемой мощностью 30 ВА. Прибор относится к профессиональному медицинскому оборудованию ЛОР-кабинета и применяется по назначению врача.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -2716,7 +2678,7 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Что такое массажеры</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr"/>
@@ -3075,7 +3037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -3401,12 +3363,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>Тип и назначение</t>
+          <t>Уточните назначение прибора</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Определите задачи, под которые подбирается массажеры: профиль отделения, поток и характер исследований или процедур.</t>
+          <t>Аппарат для массажа барабанной перепонки проводит пневмомассаж переменным давлением или колебаниями воздуха. Его задача — восстановление подвижности перепонки и слуховых косточек и улучшение вентиляции среднего уха. Это лечебная процедура, а не бытовой массажёр.</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr"/>
@@ -3446,12 +3408,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>Совместимость с оборудованием</t>
+          <t>Определите формат использования</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Проверьте совместимость с имеющейся техникой, платформой и разъёмами — это исключит лишние затраты на дооснащение.</t>
+          <t>Для ЛПУ, поликлиники или физиотерапевтического кабинета нужен сертифицированный медицинский прибор. Chammed XCM3 extreme рассчитан на профессиональное применение. Определите, где и в каком объёме будут проводить процедуры, чтобы подобрать модель под нагрузку кабинета.</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr"/>
@@ -3491,12 +3453,12 @@
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>Ключевые характеристики</t>
+          <t>Проверьте режимы и таймер</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Сравните ключевые параметры моделей: Страна производства, Полная потребляемая мощность, ВА, Производитель, Скорость. Значения — в таблице сравнения и карточках товаров.</t>
+          <t>Настраиваемый режим и таймер задают длительность и интенсивность воздействия. У Chammed XCM3 extreme таймер работает в диапазоне 1–10 минут, что позволяет дозировать процедуру. Сверьте параметры с лечебными протоколами, по которым работает кабинет.</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr"/>
@@ -3536,12 +3498,12 @@
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>Бренд и качество</t>
+          <t>Оцените электропитание и размещение</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Выбор бренда влияет на ресурс, сервис и совместимость.</t>
+          <t>Полная потребляемая мощность Chammed XCM3 extreme — 30 ВА, прибор компактно размещается на рабочем месте ЛОР-врача или в физиокабинете. Убедитесь, что розеточная сеть и рабочее пространство соответствуют требованиям к установке медтехники.</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr"/>
@@ -3581,12 +3543,12 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>Регистрация и допуск</t>
+          <t>Проверьте регистрационное удостоверение</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Для клиники с медицинской лицензией необходимо действующее регистрационное удостоверение (РУ) Росздравнадзора на модель.</t>
+          <t>Для применения в медицинской организации прибор должен иметь действующее регистрационное удостоверение Росздравнадзора. Перед закупкой проверьте наличие РУ на конкретную модель и её нахождение в реестре — это условие законной эксплуатации.</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr"/>
@@ -3626,12 +3588,12 @@
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>Гарантия и сервис</t>
+          <t>Согласуйте показания с врачом</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте гарантию, наличие сервисной поддержки и поставку расходных материалов до закупки.</t>
+          <t>Пневмомассаж имеет противопоказания, среди которых острый гнойный отит и перфорация барабанной перепонки. Показания, режим и курс процедур определяет врач-оториноларинголог после осмотра. Прибор закупают под клинические задачи кабинета, а не для самостоятельного применения.</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
@@ -3681,7 +3643,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>Массажеры подбирают под задачи отделения и совместимость с имеющимся оборудованием. При выборе обращают внимание на страна производства, полная потребляемая мощность, производитель, скорость, а также на наличие регистрационного удостоверения и условия сервиса. Поможем сравнить модели и подобрать оптимальную под ваш поток исследований и бюджет.</t>
+          <t>Аппарат для пневмомассажа барабанной перепонки берут для оснащённого ЛОР- или физиотерапевтического кабинета, а не для самолечения. При выборе смотрите на регулировку режима и таймер процедуры — у Chammed XCM3 extreme он настраивается от одной до десяти минут. Прибор эффективен как часть лечебной схемы при нарушениях подвижности слуховых косточек, но у процедуры есть противопоказания, поэтому назначение всегда остаётся за врачом.</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
@@ -3965,13 +3927,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>Что такое массажеры</t>
+          <t>Коротко о категории</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>Массажеры — медицинское оборудование для оснащения клиник и медицинских учреждений. В каталоге Medford представлены модели ведущих производителей. Подберём вариант под задачи вашего отделения.</t>
+          <t>Аппарат для массажа барабанной перепонки проводит пневмомассаж — воздействие переменным давлением или звуковыми колебаниями для улучшения подвижности перепонки, слуховых косточек и вентиляции среднего уха. Это профессиональное медицинское оборудование ЛОР- и физиотерапевтического кабинета, которое имеет противопоказания и применяется по назначению врача. В каталоге представлен Chammed XCM3 extreme (Южная Корея) с настраиваемым таймером процедуры 1–10 минут и полной потребляемой мощностью 30 ВА. Показания, режим и курс процедур определяет врач-оториноларинголог после осмотра пациента.</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -4008,13 +3970,13 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>Как выбрать и на что смотреть</t>
+          <t>Что такое аппарат для массажа барабанной перепонки</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>При выборе оценивают назначение и совместимость с имеющимся оборудованием, ключевые характеристики (Страна производства, Полная потребляемая мощность, ВА, Производитель, Скорость), бренд, наличие РУ, гарантию и сервис.</t>
+          <t>Это медицинский прибор для пневмомассажа — воздействия на барабанную перепонку переменным давлением или колебаниями воздуха. Цель процедуры — восстановить подвижность перепонки и слуховых косточек и улучшить вентиляцию среднего уха. Прибор относится к профессиональному оснащению ЛОР- и физиотерапевтических кабинетов.</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -4051,13 +4013,13 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>Оснащение и совместимость</t>
+          <t>Как работает пневмомассаж</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>Уточняйте комплектацию, совместимость с вашей техникой и наличие расходных материалов. Специалисты Medford помогут собрать рабочее решение под ваш профиль.</t>
+          <t>Аппарат создаёт у наружного слухового прохода переменное давление или звуковые колебания, которые передаются на барабанную перепонку. Дозированное воздействие тренирует подвижность перепонки и цепи слуховых косточек. Длительность задают таймером: у Chammed XCM3 extreme он настраивается в диапазоне от 1 до 10 минут.</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
@@ -4094,13 +4056,13 @@
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>Оплата и доставка</t>
+          <t>Где применяют прибор</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>Оплата — по счёту для юридических лиц и ИП. Доставка по всей России, монтаж и ввод в эксплуатацию. Гарантийное и постгарантийное обслуживание, обучение персонала. Телефон для консультаций: +7 (499) 495-48-21.</t>
+          <t>Аппараты для пневмомассажа используют в ЛОР-кабинетах, поликлиниках и физиотерапевтических кабинетах как часть лечебных схем при нарушениях подвижности слуховых косточек и вентиляции среднего уха. Это сертифицированное медицинское оборудование, применяемое по назначению врача, а не для домашнего самолечения.</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
@@ -4117,6 +4079,49 @@
       <c r="K24" s="3" t="inlineStr"/>
       <c r="L24" s="3" t="inlineStr"/>
       <c r="M24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>SEO_05</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>550</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>Как выбрать модель для кабинета</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr"/>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Определите формат применения и нагрузку кабинета, проверьте настраиваемый режим и таймер, параметры электропитания и наличие регистрационного удостоверения Росздравнадзора. Chammed XCM3 extreme (Южная Корея) с таймером 1–10 минут и мощностью 30 ВА подходит для профессионального ЛОР-приёма. Показания к процедуре определяет врач.</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>massazhery</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr"/>
+      <c r="K25" s="3" t="inlineStr"/>
+      <c r="L25" s="3" t="inlineStr"/>
+      <c r="M25" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
